--- a/out/LSTM-mamba2_repeat_2_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>3.1133722983876</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>3.1133722983876</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.424137072939437</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.424137072939437</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.443559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.043559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.043559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.043559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.043559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.043559541701984</v>
+        <v>3.1133722983876</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.043559541701984</v>
+        <v>3.1133722983876</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.043559541701984</v>
+        <v>3.1133722983876</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.043559541701984</v>
+        <v>3.1133722983876</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.443559541701984</v>
+        <v>3.1133722983876</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.043559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.043559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.043559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.043559541701984</v>
+        <v>3.7133722983876</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.2742121623455775</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-2.859845357423183e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.01231366378405696</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.02466018948112707</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.04757419531906017</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.1075264055260986</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.0146340891673684</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.08916016362508224</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.002966125049543661</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.08043887866969569</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.002568091184858326</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.082605896265656</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.001252931856672656</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.08254101490166481</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.0005950181067742658</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.08247746118407441</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.0002449628811652611</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.08237156837144587</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.0001686260852558774</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.08246307411779207</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>6.716014665040973e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.08242922455543326</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>3.24176102220032e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.08242684833833319</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>9.696194420606508e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.08241363560727309</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>3.016865658702444e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.08241000458015128</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>-1.047297874682042e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.08240487608191278</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>-2.868697537608634e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.08239961605603691</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.08239432679338521</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.08238923004601803</v>
       </c>
     </row>
     <row r="61">
@@ -49432,17 +49432,17 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.08238913439288456</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.08238899888427882</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.08238903873975109</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.08238907859522338</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.08238907062412891</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.08238923004601803</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.08238913439288456</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.08238948512104084</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.08238923801711248</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.0823891981616402</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.08238913439288456</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.08238920613273466</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.08238913439288456</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.08238923801711248</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.08238933367024619</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.0823892699014903</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.08238923004601803</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.08238920613273466</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.08238895902880654</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.08238887931786175</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.0002987656925704796</v>
+        <v>0.08238892714442848</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.05812505732295643</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1164876083976966</v>
+        <v>0.08238904671084554</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.02515764830113848</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1084038956761395</v>
+        <v>0.08238903076865664</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.01453126433073911</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1121806231289038</v>
+        <v>0.08238904671084554</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.00628941207528462</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1101596829918728</v>
+        <v>0.08238903076865664</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.004853170329949232</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1135462994785165</v>
+        <v>0.08238908656631783</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.002425119413081598</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1135271624860887</v>
+        <v>0.08238908656631783</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.001210059706540799</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1135150939898745</v>
+        <v>0.08238908656631783</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.001182344136503348</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1146668849213088</v>
+        <v>0.08238923801711248</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.00100038300967326</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1154842117466861</v>
+        <v>0.08238945323666301</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0004137929106791222</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1153099212213189</v>
+        <v>0.08238936555462401</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.0001815150205693323</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1152584810062666</v>
+        <v>0.08238931772805727</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>9.991680434550034e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.115276136115775</v>
+        <v>0.08238936555462401</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>2.548458172534854e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1152270112533458</v>
+        <v>0.0823891822194513</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>1.071998261153082e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1152229050002599</v>
+        <v>0.08238919019054575</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>3.098837180193685e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1152183515867577</v>
+        <v>0.0823891981616402</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-8.311584726890198e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1152135747365267</v>
+        <v>0.08238920613273466</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-3.054540620588209e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1152085672777633</v>
+        <v>0.08238920613273466</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-3.729078343098217e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1152038816680848</v>
+        <v>0.08238924598820693</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-4.23715470518736e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1151991343633342</v>
+        <v>0.08238930975696282</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>-4.507115944527151e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1151943562301779</v>
+        <v>0.08238942135228519</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1151944040567447</v>
+        <v>0.08238946917885193</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1151943642012724</v>
+        <v>0.08238942932337964</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1151942924614223</v>
+        <v>0.08238935758352955</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1151944120278391</v>
+        <v>0.08238947714994638</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.11519425260595</v>
+        <v>0.08238931772805727</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1151940214442106</v>
+        <v>0.08238908656631783</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1151939736176438</v>
+        <v>0.08238903873975109</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1151940055020216</v>
+        <v>0.08238907062412891</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1151940692707773</v>
+        <v>0.08238913439288456</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1151940692707773</v>
+        <v>0.08238913439288456</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1151939895598327</v>
+        <v>0.08238905468194001</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1151862814750522</v>
+        <v>0.08238893511552293</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1139832931201092</v>
+        <v>0.08238889526005067</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.09159209438542068</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2987021580495571</v>
+        <v>0.08238903873975109</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.08950941494301838</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3858455108691945</v>
+        <v>0.08238917424835684</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.04218333289796149</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3804914552745163</v>
+        <v>0.08238915830616793</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.01916313551882014</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3765296899622509</v>
+        <v>0.08238913439288456</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.007974458650942838</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3732635749775318</v>
+        <v>0.08238909453741228</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.001897062604553745</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3690574100496955</v>
+        <v>0.08238899091318436</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.0005143505677898483</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3666246013908975</v>
+        <v>0.0823888713467673</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3666246013908975</v>
+        <v>0.08238899091318436</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3666246013908975</v>
+        <v>0.08238903873975109</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3662528548823343</v>
+        <v>0.08238913439288456</v>
       </c>
     </row>
     <row r="125">
@@ -100308,21 +100308,21 @@
         <v>0</v>
       </c>
       <c r="IY125" t="n">
-        <v>-0.1098662323770395</v>
+        <v>0</v>
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2563866225052951</v>
+        <v>0.08238901482646772</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-8.119180235081484e-06</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2563811026419224</v>
+        <v>0.08238902279756218</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_2_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.443559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.443559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.043559541701984</v>
+        <v>0.5001101738204644</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-3.377452498895582e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.01454232985363402</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.02912346934078063</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.05618388360584521</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.1269877515306145</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.01728298655961136</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.1052970601390631</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.003503961934120857</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.09499805171393626</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.003033452695753682</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.09755819676278694</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.001480437618174389</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.09748246949372558</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.0007039300793847394</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.09740829321620893</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.000290613117814596</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.09728410652046371</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.0001994929448569223</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.09739298406348842</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>8.069017414736156e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.09735387665898212</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>3.909932633307521e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.09735196470431355</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>1.232051485285767e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.09733731103551062</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>4.73476544271011e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.09733391528460314</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>-4.826261424937623e-07</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.09732876956820093</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>-2.868697537608634e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.09732347765794699</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.09731811665544519</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.09731297208151152</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.09730777979579451</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.09730764428718877</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.09730768414266106</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.09730772399813332</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.09730771602703887</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.09730787544892798</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.09730777979579451</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.09730813052395079</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.09730788342002243</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.09730784356455016</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.09730777979579451</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.09730785153564461</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.09730777979579451</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.09730788342002243</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.09730797907315614</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.09730791530440026</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.09730787544892798</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.09730785153564461</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.09730760443171649</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.04463666190242516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.0973075247207717</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204645</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.0002987656925704796</v>
+        <v>0.09730757254733843</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.05812505732295643</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1164876083976966</v>
+        <v>0.09730769211375551</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.02515764830113848</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1084038956761395</v>
+        <v>0.09730767617156659</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.01453126433073911</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.0446366619024251</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1121806231289038</v>
+        <v>0.09730769211375551</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.00628941207528462</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1101596829918728</v>
+        <v>0.09730767617156659</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.004853170329949232</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1135462994785165</v>
+        <v>0.09730773196922778</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.002425119413081598</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1135271624860887</v>
+        <v>0.09730773196922778</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.001210059706540799</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1135150939898745</v>
+        <v>0.09730773196922778</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.001182344136503348</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1146668849213088</v>
+        <v>0.09730788342002243</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.00100038300967326</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1154842117466861</v>
+        <v>0.09730809863957297</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0004137929106791222</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1153099212213189</v>
+        <v>0.09730801095753396</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.0001815150205693323</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1152584810062666</v>
+        <v>0.09730796313096722</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>9.991680434550034e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.115276136115775</v>
+        <v>0.09730801095753396</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>2.548458172534854e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1152270112533458</v>
+        <v>0.09730782762236125</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>1.071998261153082e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242505</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1152229050002599</v>
+        <v>0.09730783559345571</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>3.098837180193685e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1152183515867577</v>
+        <v>0.09730784356455016</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-8.311584726890198e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1152135747365267</v>
+        <v>0.09730785153564461</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-3.054540620588209e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1152085672777633</v>
+        <v>0.09730785153564461</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-3.729078343098217e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1152038816680848</v>
+        <v>0.0973078913911169</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-4.23715470518736e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1151991343633342</v>
+        <v>0.09730795515987277</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>-4.507115944527151e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1151943562301779</v>
+        <v>0.09730806675519516</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1151944040567447</v>
+        <v>0.09730811458176188</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1151943642012724</v>
+        <v>0.09730807472628961</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1151942924614223</v>
+        <v>0.0973080029864395</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1151944120278391</v>
+        <v>0.09730812255285634</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.11519425260595</v>
+        <v>0.09730796313096722</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1151940214442106</v>
+        <v>0.09730773196922778</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1151939736176438</v>
+        <v>0.09730768414266106</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1151940055020216</v>
+        <v>0.09730771602703887</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1151940692707773</v>
+        <v>0.09730777979579451</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1151940692707773</v>
+        <v>0.09730777979579451</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1151939895598327</v>
+        <v>0.09730770008484996</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1151862814750522</v>
+        <v>0.0973075805184329</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1139832931201092</v>
+        <v>0.09730754066296061</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.09159209438542068</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2987021580495571</v>
+        <v>0.09730768414266106</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.08950941494301838</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3858455108691945</v>
+        <v>0.09730781965126679</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.04218333289796149</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3804914552745163</v>
+        <v>0.09730780370907788</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.01916313551882014</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3765296899622509</v>
+        <v>0.09730777979579451</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.007974458650942838</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3732635749775318</v>
+        <v>0.09730773994032224</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.001897062604553745</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975752</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3690574100496955</v>
+        <v>0.09730763631609432</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.0005143505677898483</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3666246013908975</v>
+        <v>0.09730751674967725</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3666246013908975</v>
+        <v>0.09730763631609432</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975752</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3666246013908975</v>
+        <v>0.09730768414266106</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204642</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3662528548823343</v>
+        <v>0.09730777979579451</v>
       </c>
     </row>
     <row r="125">
@@ -100308,21 +100308,21 @@
         <v>0</v>
       </c>
       <c r="IY125" t="n">
-        <v>-0.1098662323770395</v>
+        <v>0</v>
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.043559541701984</v>
+        <v>0.5001101738204642</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2563866225052951</v>
+        <v>0.09730766022937769</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-8.119180235081484e-06</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.3723734178614444</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2563811026419224</v>
+        <v>0.09730766820047214</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_2_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.3396479487419128</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.2151575535535812</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.08679664134979248</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01278851181268692</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01435329392552376</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5001101738204643</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.009714741259813309</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.02611001953482628</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.03512837365269661</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.03186896443367004</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.03801383450627327</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.03380459547042847</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.03729419037699699</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0313393697142601</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0137561708688736</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0001720935106277466</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5001101738204643</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.009677705354988575</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001345202326774597</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001522088423371315</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5001101738204643</v>
+        <v>-0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.002793325111269951</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01008809730410576</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01361434534192085</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.008672546595335007</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0009439606219530106</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0030258409678936</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004585660994052887</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5001101738204643</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01060109958052635</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01440225914120674</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.355583685738504</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.02326695248484612</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0191623754799366</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.004860557615756989</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7001101738204645</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.008739139884710312</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5001101738204644</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.00806085392832756</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02341676503419876</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.355583685738504</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0298524871468544</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.03570839017629623</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.03149273246526718</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.02631183713674545</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0211455337703228</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>6.725266575813293e-05</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.5001101738204644</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.02757191471755505</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.05060245096683502</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.07646827399730682</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-3.377452498895582e-05</v>
+        <v>-1.832464563928079e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.01454232985363402</v>
+        <v>0.007889953300800185</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.08354057371616364</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.02912346934078063</v>
+        <v>0.01580117777179286</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.05618388360584521</v>
+        <v>0.03048388960583396</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.08901984989643097</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1269877515306145</v>
+        <v>0.06889896671024384</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.01728298655961136</v>
+        <v>0.00937620908896813</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.112533912062645</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1052970601390631</v>
+        <v>0.05712971148819337</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.003503961934120857</v>
+        <v>0.001898719333956945</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.08928389847278595</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.09499805171393626</v>
+        <v>0.05153961946045398</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.003033452695753682</v>
+        <v>0.001643811630141548</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.07861866801977158</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.09755819676278694</v>
+        <v>0.05292642706298525</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.001480437618174389</v>
+        <v>0.0008007204045799818</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.06925727427005768</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.09748246949372558</v>
+        <v>0.052883056390716</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0007039300793847394</v>
+        <v>0.0003798668479977473</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.06253309547901154</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.09740829321620893</v>
+        <v>0.05284051900103851</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.000290613117814596</v>
+        <v>0.0001553325384757131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.05215470492839813</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.09728410652046371</v>
+        <v>0.05277087536944775</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0001994929448569223</v>
+        <v>0.0001061206945637616</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.04152176901698112</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.09739298406348842</v>
+        <v>0.05282763904710929</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>8.069017414736156e-05</v>
+        <v>4.138866570383483e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.05429184064269066</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.09735387665898212</v>
+        <v>0.05280417488827859</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>3.909932633307521e-05</v>
+        <v>1.905417799985921e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.06469531357288361</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.09735196470431355</v>
+        <v>0.05280084623303218</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>1.232051485285767e-05</v>
+        <v>4.447553556104185e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.04190577939152718</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.09733731103551062</v>
+        <v>0.05279065885715792</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.73476544271011e-06</v>
+        <v>1.536993520230006e-07</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.02477959915995598</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.09733391528460314</v>
+        <v>0.05278650816550106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-4.826261424937623e-07</v>
+        <v>-2.741313071246881e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.005862407386302948</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.09732876956820093</v>
+        <v>0.05278143132175273</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.868697537608634e-06</v>
+        <v>-3.934348768804317e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.005280021578073502</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.09732347765794699</v>
+        <v>0.05277626942443685</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.077656293461284e-06</v>
+        <v>-4.538828146730642e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01028189994394779</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.09731811665544519</v>
+        <v>0.05277105305326101</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01471306756138802</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.09731297208151152</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02699259109795094</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.09730777979579451</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.02086833864450455</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.09730764428718877</v>
+        <v>0.05276572514415463</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.02450806275010109</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.09730768414266106</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.011796317063272</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.09730772399813332</v>
+        <v>0.05276580485509918</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01764628104865551</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.09730771602703887</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01723689772188663</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.09730787544892798</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0320214182138443</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.09730777979579451</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.03234955668449402</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.09730813052395079</v>
+        <v>0.05276621138091665</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02237213775515556</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.09730788342002243</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02438574098050594</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.09730784356455016</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.009094653651118279</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.09730777979579451</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.006062185391783714</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.09730785153564461</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01019651256501675</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.09730777979579451</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.079662024974823</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.09730788342002243</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.07194656878709793</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.09730797907315614</v>
+        <v>0.05276605993012199</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.03613906726241112</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.09730791530440026</v>
+        <v>0.05276599616136612</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.008639376610517502</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.09730787544892798</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02392269670963287</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.09730785153564461</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02047760784626007</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.09730760443171649</v>
+        <v>0.05276568528868235</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.005581529811024666</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.04463666190242516</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.0973075247207717</v>
+        <v>0.05276560557773756</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.001369137316942215</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7001101738204645</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.09730757254733843</v>
+        <v>0.05276565340430429</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.007481101900339127</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.09730769211375551</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>2.282485365867615e-05</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.09730767617156659</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002149729058146477</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.0446366619024251</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.09730769211375551</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.004457341507077217</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6108368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.09730767617156659</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003261318430304527</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.09730773196922778</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.007756728678941727</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.09730773196922778</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01941176131367683</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.155363338097575</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.09730773196922778</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.007166644558310509</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.09730788342002243</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.03603821992874146</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.09730809863957297</v>
+        <v>0.05276617949653883</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01435147412121296</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.09730801095753396</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.0002719294279813766</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.09730796313096722</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01228336989879608</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.09730801095753396</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001736937090754509</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1553633380975749</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.09730782762236125</v>
+        <v>0.05276590847932711</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.003373993560671806</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.04463666190242505</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.09730783559345571</v>
+        <v>0.05276591645042156</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.000745818018913269</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.09730784356455016</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.006136395037174225</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.09730785153564461</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.009049683809280396</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.09730785153564461</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.02172724902629852</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.044636661902425</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.0973078913911169</v>
+        <v>0.05276597224808275</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02101584896445274</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.09730795515987277</v>
+        <v>0.05276603601683862</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02002672478556633</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.09730806675519516</v>
+        <v>0.052766147612161</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005814606323838234</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.09730811458176188</v>
+        <v>0.05276619543872774</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.008717687800526619</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.09730807472628961</v>
+        <v>0.05276615558325546</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01094772946089506</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.0973080029864395</v>
+        <v>0.05276608384340536</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.019893579185009</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.09730812255285634</v>
+        <v>0.05276620340982219</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.03713414445519447</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.09730796313096722</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02313759922981262</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.09730773196922778</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.0107113029807806</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.044636661902425</v>
+        <v>0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.09730768414266106</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.005505938082933426</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.09730771602703887</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.001157511025667191</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.09730777979579451</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.005367744714021683</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.09730777979579451</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.004379421472549438</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.09730770008484996</v>
+        <v>0.05276578094181581</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.001997694373130798</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.0973075805184329</v>
+        <v>0.05276566137539875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.00317000225186348</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.09730754066296061</v>
+        <v>0.05276562151992647</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0002982113510370255</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.09730768414266106</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.004717504605650902</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.09730781965126679</v>
+        <v>0.05276590050823265</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01006728783249855</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.09730780370907788</v>
+        <v>0.05276588456604374</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.006281670182943344</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.09730777979579451</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.000273803249001503</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7001101738204643</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.09730773994032224</v>
+        <v>0.05276582079728809</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01990159414708614</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1553633380975752</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.09730763631609432</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02644111961126328</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.09730751674967725</v>
+        <v>0.0527655976066431</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.008963670581579208</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.09730763631609432</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004250742495059967</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1553633380975752</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.09730768414266106</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.003733497112989426</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5001101738204642</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.09730777979579451</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.002748625352978706</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5001101738204642</v>
+        <v>0.37</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.09730766022937769</v>
+        <v>0.05276574108634353</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0135509055107832</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3723734178614444</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.09730766820047214</v>
+        <v>0.05276574905743799</v>
       </c>
     </row>
   </sheetData>
